--- a/output/pdf_financials_xlsx/IDL.xlsx
+++ b/output/pdf_financials_xlsx/IDL.xlsx
@@ -5966,34 +5966,34 @@
         <v>5.930955</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>10.104168</v>
+        <v>10.196081</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>4.053035</v>
+        <v>10.846889</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>4.630094</v>
+        <v>11.476872</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>4.630094</v>
+        <v>11.476872</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>4.630094</v>
+        <v>11.476872</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>5.084398</v>
+        <v>12.270505</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>5.507196</v>
+        <v>12.693303</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>5.507196</v>
+        <v>12.693303</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>5.508389</v>
+        <v>12.694496</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>8.123823</v>
+        <v>15.30993</v>
       </c>
       <c r="N92" s="1" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="O92" s="3" t="n">
-        <v>8.123823</v>
+        <v>15.30993</v>
       </c>
       <c r="P92" s="3" t="n">
         <v>15.30993</v>
@@ -6363,7 +6363,7 @@
         <v>-11.591034</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>3.20523</v>
+        <v>-3.20523</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>-3.89789</v>
@@ -11625,7 +11625,11 @@
           <t>Share-based payments reserve 13</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -13130,7 +13134,11 @@
           <t>Share-based payments reserve 14</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -15255,7 +15263,11 @@
           <t>Share-based payments reserve 15</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -17736,7 +17748,11 @@
           <t>Share-based payments reserve (Note 15)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -18641,7 +18657,11 @@
           <t>Share-based payments reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -20172,7 +20192,11 @@
           <t>Share-based payments reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -20374,7 +20398,11 @@
           <t>Warrants reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -21596,7 +21624,11 @@
           <t>Share-based payments reserve (Note 11) 6,216,795</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -21800,7 +21832,11 @@
           <t>Warrants reserve (Note 13) 577,059</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -22200,7 +22236,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E137" s="5" t="n">
         <v>0.450676</v>
       </c>
@@ -27028,7 +27068,7 @@
         <v>-11.591034</v>
       </c>
       <c r="O185" s="5" t="n">
-        <v>3.20523</v>
+        <v>-3.20523</v>
       </c>
       <c r="P185" s="5" t="n">
         <v>-3.89789</v>

--- a/output/pdf_financials_xlsx/IDL.xlsx
+++ b/output/pdf_financials_xlsx/IDL.xlsx
@@ -2445,10 +2445,10 @@
         <v>0.028365</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.11047</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.021778</v>
       </c>
     </row>
     <row r="35">
@@ -2565,10 +2565,10 @@
         <v>0.028365</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.11047</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.021778</v>
       </c>
     </row>
     <row r="37">
@@ -3285,10 +3285,10 @@
         <v>0.022637</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.12836</v>
+        <v>0.01789</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.045115</v>
+        <v>0.023337</v>
       </c>
     </row>
     <row r="49">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -42705,7 +42705,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -48424,7 +48424,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">

--- a/output/pdf_financials_xlsx/IDL.xlsx
+++ b/output/pdf_financials_xlsx/IDL.xlsx
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.169687</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.13656</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.107198</v>
@@ -2109,19 +2109,19 @@
         <v>0.07726</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.065842</v>
+        <v>0.110986</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.081205</v>
+        <v>0.119462</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.061638</v>
+        <v>0.169552</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.078791</v>
+        <v>0.214513</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.094094</v>
+        <v>0.249527</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>0.06418699999999999</v>
@@ -2132,16 +2132,16 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.06329700000000001</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.077195</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.07079000000000001</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.027706</v>
       </c>
     </row>
     <row r="29">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-15.69931</v>
+        <v>-15.529623</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.970502</v>
+        <v>-5.833942</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-4.107742</v>
@@ -2169,19 +2169,19 @@
         <v>-1.884557</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.31239</v>
+        <v>-1.267246</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.845703</v>
+        <v>-3.807446</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.767399</v>
+        <v>-5.659485</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-19.080741</v>
+        <v>-18.945019</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>11.475623</v>
+        <v>11.631056</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-3.833678</v>
@@ -2192,16 +2192,16 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.693744</v>
+        <v>-0.630447</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.595047</v>
+        <v>-0.517852</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.474132</v>
+        <v>-1.403342</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.569814</v>
+        <v>-0.542108</v>
       </c>
     </row>
     <row r="30">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-93.02203356287677</v>
+        <v>-92.01659894127978</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-61.27775651539723</v>
+        <v>-59.87618418031676</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-75.95416946720573</v>
@@ -2229,19 +2229,19 @@
         <v>-63.11943597816258</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-51.54071547258255</v>
+        <v>-49.76780188798174</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-157.8911649252546</v>
+        <v>-156.3204658108025</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-76.45826392754586</v>
+        <v>-75.02765073545056</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-2180.22007027166</v>
+        <v>-2164.712086154198</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>1532.780760805685</v>
+        <v>1553.54170005877</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>-563.8458280140487</v>
@@ -2252,16 +2252,16 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-273.8553241882957</v>
+        <v>-248.8688443698806</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-266.3546758339153</v>
+        <v>-231.8006839626864</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-2337.517442597996</v>
+        <v>-2225.266396042116</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-527.8890515276722</v>
+        <v>-502.2215634322136</v>
       </c>
     </row>
     <row r="31">
@@ -6397,49 +6397,49 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.107198</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.08552899999999999</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.069536</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.07726</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.065842</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.119462</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.169552</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.078791</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.094094</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.06418699999999999</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.06329700000000001</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.077195</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.07079000000000001</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.027706</v>
       </c>
     </row>
     <row r="101">
@@ -7573,16 +7573,16 @@
         <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>1.281314</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>0.866174</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>2.244086</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>1.955635</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
@@ -23838,7 +23838,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -25648,7 +25652,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -28497,7 +28505,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -31416,7 +31424,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -32717,7 +32725,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -33319,7 +33331,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -33420,7 +33436,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -34527,7 +34543,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -35945,7 +35965,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -38149,7 +38169,11 @@
           <t>Issuance of shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -48020,7 +48044,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -48121,7 +48149,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -50416,7 +50444,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -50517,7 +50549,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -53121,7 +53153,11 @@
           <t>Depreciation of property, plant and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
           <t>-</t>
@@ -53222,7 +53258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -56018,7 +56054,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E475" s="5" t="n">
@@ -62208,7 +62244,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">

--- a/output/pdf_financials_xlsx/IDL.xlsx
+++ b/output/pdf_financials_xlsx/IDL.xlsx
@@ -4270,7 +4270,7 @@
         <v>2.317683</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>4.311686</v>
       </c>
       <c r="K64" s="3" t="n">
         <v>0</v>
@@ -4510,7 +4510,7 @@
         <v>2.317683</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>4.311686</v>
       </c>
       <c r="K68" s="3" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
         <v>5.022455</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>4.555919</v>
+        <v>0.244233</v>
       </c>
       <c r="K75" s="3" t="n">
         <v>37.298985</v>
@@ -7001,25 +7001,25 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.493425</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.952512</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.037045</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.035218</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.043023</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.01916</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.002833</v>
       </c>
     </row>
     <row r="111">
@@ -7111,7 +7111,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.010161</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -24040,7 +24040,11 @@
           <t>Lease accretion expense 7</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -25852,7 +25856,11 @@
           <t>Lease accretion expense</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -28806,7 +28814,11 @@
           <t>Debenture Accretion expense</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -28905,7 +28917,11 @@
           <t>Lease Accretion expense</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -34139,7 +34155,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -34648,7 +34668,11 @@
           <t>Proceeds on disposition of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -36357,7 +36381,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -40599,7 +40627,11 @@
           <t>Proceeds from share issuances, net</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E320" s="5" t="n">
         <v>8.31622</v>
       </c>
